--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1387,6 +1387,1847 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120170118</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>876442</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7396355</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120170135</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>876452</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7396372</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120170137</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>876569</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7396417</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120170108</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>876568</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7396419</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120170105</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>876569</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7396418</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120170125</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>876716</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7396410</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120170120</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>876442</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7396374</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120170134</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>876433</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7396336</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120170121</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>876428</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7396353</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120170123</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>876887</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7396501</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120170138</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>876628</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7396416</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120170102</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>876516</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7396355</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120170122</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>876931</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7396534</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120170140</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>876678</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7396446</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120170117</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>876887</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7396479</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120170119</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>876440</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7396356</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120170136</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>876566</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7396402</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120170139</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>876641</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7396423</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134330</v>
+        <v>120134339</v>
       </c>
       <c r="B2" t="n">
-        <v>96868</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876589</v>
+        <v>876579</v>
       </c>
       <c r="R2" t="n">
-        <v>7396375</v>
+        <v>7396370</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134337</v>
+        <v>120134331</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876530</v>
+        <v>876885</v>
       </c>
       <c r="R3" t="n">
-        <v>7396367</v>
+        <v>7396474</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134331</v>
+        <v>120134330</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>96868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876885</v>
+        <v>876589</v>
       </c>
       <c r="R4" t="n">
-        <v>7396474</v>
+        <v>7396375</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120134339</v>
+        <v>120134337</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876579</v>
+        <v>876530</v>
       </c>
       <c r="R8" t="n">
-        <v>7396370</v>
+        <v>7396367</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170118</v>
+        <v>120170102</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876442</v>
+        <v>876516</v>
       </c>
       <c r="R9" t="n">
         <v>7396355</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170135</v>
+        <v>120170123</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876452</v>
+        <v>876887</v>
       </c>
       <c r="R10" t="n">
-        <v>7396372</v>
+        <v>7396501</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170108</v>
+        <v>120170136</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876568</v>
+        <v>876566</v>
       </c>
       <c r="R12" t="n">
-        <v>7396419</v>
+        <v>7396402</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1771,11 +1771,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170105</v>
+        <v>120170121</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
+        <v>90576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876569</v>
+        <v>876428</v>
       </c>
       <c r="R13" t="n">
-        <v>7396418</v>
+        <v>7396353</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1904,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170125</v>
+        <v>120170135</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876716</v>
+        <v>876452</v>
       </c>
       <c r="R14" t="n">
-        <v>7396410</v>
+        <v>7396372</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170120</v>
+        <v>120170140</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876442</v>
+        <v>876678</v>
       </c>
       <c r="R15" t="n">
-        <v>7396374</v>
+        <v>7396446</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2108,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170134</v>
+        <v>120170139</v>
       </c>
       <c r="B16" t="n">
         <v>78526</v>
@@ -2148,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876433</v>
+        <v>876641</v>
       </c>
       <c r="R16" t="n">
-        <v>7396336</v>
+        <v>7396423</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170121</v>
+        <v>120170134</v>
       </c>
       <c r="B17" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876428</v>
+        <v>876433</v>
       </c>
       <c r="R17" t="n">
-        <v>7396353</v>
+        <v>7396336</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2312,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170123</v>
+        <v>120170108</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876887</v>
+        <v>876568</v>
       </c>
       <c r="R18" t="n">
-        <v>7396501</v>
+        <v>7396419</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2388,6 +2383,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170138</v>
+        <v>120170118</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876628</v>
+        <v>876442</v>
       </c>
       <c r="R19" t="n">
-        <v>7396416</v>
+        <v>7396355</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170102</v>
+        <v>120170119</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876516</v>
+        <v>876440</v>
       </c>
       <c r="R20" t="n">
-        <v>7396355</v>
+        <v>7396356</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120170122</v>
+        <v>120170138</v>
       </c>
       <c r="B21" t="n">
         <v>78526</v>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>876931</v>
+        <v>876628</v>
       </c>
       <c r="R21" t="n">
-        <v>7396534</v>
+        <v>7396416</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120170140</v>
+        <v>120170122</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>876678</v>
+        <v>876931</v>
       </c>
       <c r="R22" t="n">
-        <v>7396446</v>
+        <v>7396534</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120170119</v>
+        <v>120170125</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>876440</v>
+        <v>876716</v>
       </c>
       <c r="R24" t="n">
-        <v>7396356</v>
+        <v>7396410</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120170136</v>
+        <v>120170120</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>876566</v>
+        <v>876442</v>
       </c>
       <c r="R25" t="n">
-        <v>7396402</v>
+        <v>7396374</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120170139</v>
+        <v>120170105</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>876641</v>
+        <v>876569</v>
       </c>
       <c r="R26" t="n">
-        <v>7396423</v>
+        <v>7396418</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134339</v>
+        <v>120134337</v>
       </c>
       <c r="B2" t="n">
         <v>78526</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876579</v>
+        <v>876530</v>
       </c>
       <c r="R2" t="n">
-        <v>7396370</v>
+        <v>7396367</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134331</v>
+        <v>120134339</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876885</v>
+        <v>876579</v>
       </c>
       <c r="R3" t="n">
-        <v>7396474</v>
+        <v>7396370</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134330</v>
+        <v>120134340</v>
       </c>
       <c r="B4" t="n">
-        <v>96868</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876589</v>
+        <v>876586</v>
       </c>
       <c r="R4" t="n">
-        <v>7396375</v>
+        <v>7396380</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134341</v>
+        <v>120134330</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>96868</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876700</v>
+        <v>876589</v>
       </c>
       <c r="R5" t="n">
-        <v>7396427</v>
+        <v>7396375</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134340</v>
+        <v>120134331</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876586</v>
+        <v>876885</v>
       </c>
       <c r="R6" t="n">
-        <v>7396380</v>
+        <v>7396474</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120134337</v>
+        <v>120134341</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876530</v>
+        <v>876700</v>
       </c>
       <c r="R8" t="n">
-        <v>7396367</v>
+        <v>7396427</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170102</v>
+        <v>120170121</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>90576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876516</v>
+        <v>876428</v>
       </c>
       <c r="R9" t="n">
-        <v>7396355</v>
+        <v>7396353</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170123</v>
+        <v>120170138</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876887</v>
+        <v>876628</v>
       </c>
       <c r="R10" t="n">
-        <v>7396501</v>
+        <v>7396416</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170137</v>
+        <v>120170120</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876569</v>
+        <v>876442</v>
       </c>
       <c r="R11" t="n">
-        <v>7396417</v>
+        <v>7396374</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170136</v>
+        <v>120170137</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876566</v>
+        <v>876569</v>
       </c>
       <c r="R12" t="n">
-        <v>7396402</v>
+        <v>7396417</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170121</v>
+        <v>120170108</v>
       </c>
       <c r="B13" t="n">
-        <v>90576</v>
+        <v>57326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876428</v>
+        <v>876568</v>
       </c>
       <c r="R13" t="n">
-        <v>7396353</v>
+        <v>7396419</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1873,6 +1873,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170135</v>
+        <v>120170125</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876452</v>
+        <v>876716</v>
       </c>
       <c r="R14" t="n">
-        <v>7396372</v>
+        <v>7396410</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2001,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170140</v>
+        <v>120170135</v>
       </c>
       <c r="B15" t="n">
         <v>78526</v>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876678</v>
+        <v>876452</v>
       </c>
       <c r="R15" t="n">
-        <v>7396446</v>
+        <v>7396372</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2103,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170139</v>
+        <v>120170123</v>
       </c>
       <c r="B16" t="n">
         <v>78526</v>
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876641</v>
+        <v>876887</v>
       </c>
       <c r="R16" t="n">
-        <v>7396423</v>
+        <v>7396501</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170134</v>
+        <v>120170102</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876433</v>
+        <v>876516</v>
       </c>
       <c r="R17" t="n">
-        <v>7396336</v>
+        <v>7396355</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2307,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170108</v>
+        <v>120170140</v>
       </c>
       <c r="B18" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876568</v>
+        <v>876678</v>
       </c>
       <c r="R18" t="n">
-        <v>7396419</v>
+        <v>7396446</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2383,11 +2388,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170119</v>
+        <v>120170117</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876440</v>
+        <v>876887</v>
       </c>
       <c r="R20" t="n">
-        <v>7396356</v>
+        <v>7396479</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120170138</v>
+        <v>120170136</v>
       </c>
       <c r="B21" t="n">
         <v>78526</v>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>876628</v>
+        <v>876566</v>
       </c>
       <c r="R21" t="n">
-        <v>7396416</v>
+        <v>7396402</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120170122</v>
+        <v>120170139</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>876931</v>
+        <v>876641</v>
       </c>
       <c r="R22" t="n">
-        <v>7396534</v>
+        <v>7396423</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120170117</v>
+        <v>120170134</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>876887</v>
+        <v>876433</v>
       </c>
       <c r="R23" t="n">
-        <v>7396479</v>
+        <v>7396336</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2924,7 +2924,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120170125</v>
+        <v>120170122</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>876716</v>
+        <v>876931</v>
       </c>
       <c r="R24" t="n">
-        <v>7396410</v>
+        <v>7396534</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120170120</v>
+        <v>120170105</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>876442</v>
+        <v>876569</v>
       </c>
       <c r="R25" t="n">
-        <v>7396374</v>
+        <v>7396418</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120170105</v>
+        <v>120170119</v>
       </c>
       <c r="B26" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,25 +3140,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>876569</v>
+        <v>876440</v>
       </c>
       <c r="R26" t="n">
-        <v>7396418</v>
+        <v>7396356</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120134337</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134339</v>
+        <v>120134330</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>96891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876579</v>
+        <v>876589</v>
       </c>
       <c r="R3" t="n">
-        <v>7396370</v>
+        <v>7396375</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134340</v>
+        <v>120134329</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876586</v>
+        <v>876676</v>
       </c>
       <c r="R4" t="n">
-        <v>7396380</v>
+        <v>7396418</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134330</v>
+        <v>120134340</v>
       </c>
       <c r="B5" t="n">
-        <v>96868</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876589</v>
+        <v>876586</v>
       </c>
       <c r="R5" t="n">
-        <v>7396375</v>
+        <v>7396380</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
         <v>120134331</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134329</v>
+        <v>120134341</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876676</v>
+        <v>876700</v>
       </c>
       <c r="R7" t="n">
-        <v>7396418</v>
+        <v>7396427</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120134341</v>
+        <v>120134339</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876700</v>
+        <v>876579</v>
       </c>
       <c r="R8" t="n">
-        <v>7396427</v>
+        <v>7396370</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170121</v>
+        <v>120170139</v>
       </c>
       <c r="B9" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876428</v>
+        <v>876641</v>
       </c>
       <c r="R9" t="n">
-        <v>7396353</v>
+        <v>7396423</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170138</v>
+        <v>120170122</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876628</v>
+        <v>876931</v>
       </c>
       <c r="R10" t="n">
-        <v>7396416</v>
+        <v>7396534</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170120</v>
+        <v>120170125</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876442</v>
+        <v>876716</v>
       </c>
       <c r="R11" t="n">
-        <v>7396374</v>
+        <v>7396410</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1698,7 +1698,7 @@
         <v>120170137</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170108</v>
+        <v>120170121</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>90594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876568</v>
+        <v>876428</v>
       </c>
       <c r="R13" t="n">
-        <v>7396419</v>
+        <v>7396353</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1873,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170125</v>
+        <v>120170138</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876716</v>
+        <v>876628</v>
       </c>
       <c r="R14" t="n">
-        <v>7396410</v>
+        <v>7396416</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170135</v>
+        <v>120170136</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876452</v>
+        <v>876566</v>
       </c>
       <c r="R15" t="n">
-        <v>7396372</v>
+        <v>7396402</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170123</v>
+        <v>120170134</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876887</v>
+        <v>876433</v>
       </c>
       <c r="R16" t="n">
-        <v>7396501</v>
+        <v>7396336</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170102</v>
+        <v>120170108</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>57336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876516</v>
+        <v>876568</v>
       </c>
       <c r="R17" t="n">
-        <v>7396355</v>
+        <v>7396419</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2286,6 +2281,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170140</v>
+        <v>120170119</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876678</v>
+        <v>876440</v>
       </c>
       <c r="R18" t="n">
-        <v>7396446</v>
+        <v>7396356</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170118</v>
+        <v>120170117</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876442</v>
+        <v>876887</v>
       </c>
       <c r="R19" t="n">
-        <v>7396355</v>
+        <v>7396479</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170117</v>
+        <v>120170102</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876887</v>
+        <v>876516</v>
       </c>
       <c r="R20" t="n">
-        <v>7396479</v>
+        <v>7396355</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120170136</v>
+        <v>120170105</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>876566</v>
+        <v>876569</v>
       </c>
       <c r="R21" t="n">
-        <v>7396402</v>
+        <v>7396418</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120170139</v>
+        <v>120170123</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>876641</v>
+        <v>876887</v>
       </c>
       <c r="R22" t="n">
-        <v>7396423</v>
+        <v>7396501</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120170134</v>
+        <v>120170120</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>876433</v>
+        <v>876442</v>
       </c>
       <c r="R23" t="n">
-        <v>7396336</v>
+        <v>7396374</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120170122</v>
+        <v>120170140</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>876931</v>
+        <v>876678</v>
       </c>
       <c r="R24" t="n">
-        <v>7396534</v>
+        <v>7396446</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120170105</v>
+        <v>120170118</v>
       </c>
       <c r="B25" t="n">
-        <v>57463</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>876569</v>
+        <v>876442</v>
       </c>
       <c r="R25" t="n">
-        <v>7396418</v>
+        <v>7396355</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120170119</v>
+        <v>120170135</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,25 +3140,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>876440</v>
+        <v>876452</v>
       </c>
       <c r="R26" t="n">
-        <v>7396356</v>
+        <v>7396372</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134337</v>
+        <v>120134340</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876530</v>
+        <v>876586</v>
       </c>
       <c r="R2" t="n">
-        <v>7396367</v>
+        <v>7396380</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134330</v>
+        <v>120134337</v>
       </c>
       <c r="B3" t="n">
-        <v>96891</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876589</v>
+        <v>876530</v>
       </c>
       <c r="R3" t="n">
-        <v>7396375</v>
+        <v>7396367</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134329</v>
+        <v>120134341</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876676</v>
+        <v>876700</v>
       </c>
       <c r="R4" t="n">
-        <v>7396418</v>
+        <v>7396427</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134340</v>
+        <v>120134329</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876586</v>
+        <v>876676</v>
       </c>
       <c r="R5" t="n">
-        <v>7396380</v>
+        <v>7396418</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134331</v>
+        <v>120134330</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>96891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876885</v>
+        <v>876589</v>
       </c>
       <c r="R6" t="n">
-        <v>7396474</v>
+        <v>7396375</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134341</v>
+        <v>120134339</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876700</v>
+        <v>876579</v>
       </c>
       <c r="R7" t="n">
-        <v>7396427</v>
+        <v>7396370</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120134339</v>
+        <v>120134331</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876579</v>
+        <v>876885</v>
       </c>
       <c r="R8" t="n">
-        <v>7396370</v>
+        <v>7396474</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170139</v>
+        <v>120170118</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876641</v>
+        <v>876442</v>
       </c>
       <c r="R9" t="n">
-        <v>7396423</v>
+        <v>7396355</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170122</v>
+        <v>120170102</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876931</v>
+        <v>876516</v>
       </c>
       <c r="R10" t="n">
-        <v>7396534</v>
+        <v>7396355</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170125</v>
+        <v>120170108</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876716</v>
+        <v>876568</v>
       </c>
       <c r="R11" t="n">
-        <v>7396410</v>
+        <v>7396419</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1669,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170137</v>
+        <v>120170121</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876569</v>
+        <v>876428</v>
       </c>
       <c r="R12" t="n">
-        <v>7396417</v>
+        <v>7396353</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170121</v>
+        <v>120170125</v>
       </c>
       <c r="B13" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876428</v>
+        <v>876716</v>
       </c>
       <c r="R13" t="n">
-        <v>7396353</v>
+        <v>7396410</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170138</v>
+        <v>120170105</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876628</v>
+        <v>876569</v>
       </c>
       <c r="R14" t="n">
-        <v>7396416</v>
+        <v>7396418</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170136</v>
+        <v>120170120</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876566</v>
+        <v>876442</v>
       </c>
       <c r="R15" t="n">
-        <v>7396402</v>
+        <v>7396374</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2103,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170134</v>
+        <v>120170135</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876433</v>
+        <v>876452</v>
       </c>
       <c r="R16" t="n">
-        <v>7396336</v>
+        <v>7396372</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170108</v>
+        <v>120170138</v>
       </c>
       <c r="B17" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876568</v>
+        <v>876628</v>
       </c>
       <c r="R17" t="n">
-        <v>7396419</v>
+        <v>7396416</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2281,11 +2286,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170102</v>
+        <v>120170122</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876516</v>
+        <v>876931</v>
       </c>
       <c r="R20" t="n">
-        <v>7396355</v>
+        <v>7396534</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120170105</v>
+        <v>120170134</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>876569</v>
+        <v>876433</v>
       </c>
       <c r="R21" t="n">
-        <v>7396418</v>
+        <v>7396336</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120170123</v>
+        <v>120170139</v>
       </c>
       <c r="B22" t="n">
         <v>78542</v>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>876887</v>
+        <v>876641</v>
       </c>
       <c r="R22" t="n">
-        <v>7396501</v>
+        <v>7396423</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120170120</v>
+        <v>120170123</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>876442</v>
+        <v>876887</v>
       </c>
       <c r="R23" t="n">
-        <v>7396374</v>
+        <v>7396501</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120170118</v>
+        <v>120170137</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>876442</v>
+        <v>876569</v>
       </c>
       <c r="R25" t="n">
-        <v>7396355</v>
+        <v>7396417</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120170135</v>
+        <v>120170136</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>876452</v>
+        <v>876566</v>
       </c>
       <c r="R26" t="n">
-        <v>7396372</v>
+        <v>7396402</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170117</v>
+        <v>120170122</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876887</v>
+        <v>876931</v>
       </c>
       <c r="R19" t="n">
-        <v>7396479</v>
+        <v>7396534</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170122</v>
+        <v>120170117</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876931</v>
+        <v>876887</v>
       </c>
       <c r="R20" t="n">
-        <v>7396534</v>
+        <v>7396479</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134340</v>
+        <v>120134339</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876586</v>
+        <v>876579</v>
       </c>
       <c r="R2" t="n">
-        <v>7396380</v>
+        <v>7396370</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134337</v>
+        <v>120134330</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>96891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876530</v>
+        <v>876589</v>
       </c>
       <c r="R3" t="n">
-        <v>7396367</v>
+        <v>7396375</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134341</v>
+        <v>120134331</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876700</v>
+        <v>876885</v>
       </c>
       <c r="R4" t="n">
-        <v>7396427</v>
+        <v>7396474</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134329</v>
+        <v>120134337</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876676</v>
+        <v>876530</v>
       </c>
       <c r="R5" t="n">
-        <v>7396418</v>
+        <v>7396367</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134330</v>
+        <v>120134341</v>
       </c>
       <c r="B6" t="n">
-        <v>96891</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876589</v>
+        <v>876700</v>
       </c>
       <c r="R6" t="n">
-        <v>7396375</v>
+        <v>7396427</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134339</v>
+        <v>120134340</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876579</v>
+        <v>876586</v>
       </c>
       <c r="R7" t="n">
-        <v>7396370</v>
+        <v>7396380</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120134331</v>
+        <v>120134329</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876885</v>
+        <v>876676</v>
       </c>
       <c r="R8" t="n">
-        <v>7396474</v>
+        <v>7396418</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170118</v>
+        <v>120170125</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876442</v>
+        <v>876716</v>
       </c>
       <c r="R9" t="n">
-        <v>7396355</v>
+        <v>7396410</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170102</v>
+        <v>120170122</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876516</v>
+        <v>876931</v>
       </c>
       <c r="R10" t="n">
-        <v>7396355</v>
+        <v>7396534</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170108</v>
+        <v>120170120</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876568</v>
+        <v>876442</v>
       </c>
       <c r="R11" t="n">
-        <v>7396419</v>
+        <v>7396374</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1669,11 +1669,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170121</v>
+        <v>120170119</v>
       </c>
       <c r="B12" t="n">
-        <v>90594</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876428</v>
+        <v>876440</v>
       </c>
       <c r="R12" t="n">
-        <v>7396353</v>
+        <v>7396356</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170125</v>
+        <v>120170105</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876716</v>
+        <v>876569</v>
       </c>
       <c r="R13" t="n">
-        <v>7396410</v>
+        <v>7396418</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170105</v>
+        <v>120170134</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876569</v>
+        <v>876433</v>
       </c>
       <c r="R14" t="n">
-        <v>7396418</v>
+        <v>7396336</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170120</v>
+        <v>120170136</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876442</v>
+        <v>876566</v>
       </c>
       <c r="R15" t="n">
-        <v>7396374</v>
+        <v>7396402</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170135</v>
+        <v>120170118</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876452</v>
+        <v>876442</v>
       </c>
       <c r="R16" t="n">
-        <v>7396372</v>
+        <v>7396355</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2210,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170138</v>
+        <v>120170135</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876628</v>
+        <v>876452</v>
       </c>
       <c r="R17" t="n">
-        <v>7396416</v>
+        <v>7396372</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2312,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170119</v>
+        <v>120170137</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876440</v>
+        <v>876569</v>
       </c>
       <c r="R18" t="n">
-        <v>7396356</v>
+        <v>7396417</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2414,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170122</v>
+        <v>120170108</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876931</v>
+        <v>876568</v>
       </c>
       <c r="R19" t="n">
-        <v>7396534</v>
+        <v>7396419</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2490,6 +2485,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170117</v>
+        <v>120170139</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876887</v>
+        <v>876641</v>
       </c>
       <c r="R20" t="n">
-        <v>7396479</v>
+        <v>7396423</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120170134</v>
+        <v>120170117</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>876433</v>
+        <v>876887</v>
       </c>
       <c r="R21" t="n">
-        <v>7396336</v>
+        <v>7396479</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120170139</v>
+        <v>120170138</v>
       </c>
       <c r="B22" t="n">
         <v>78542</v>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>876641</v>
+        <v>876628</v>
       </c>
       <c r="R22" t="n">
-        <v>7396423</v>
+        <v>7396416</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120170140</v>
+        <v>120170121</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>876678</v>
+        <v>876428</v>
       </c>
       <c r="R24" t="n">
-        <v>7396446</v>
+        <v>7396353</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120170137</v>
+        <v>120170102</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>876569</v>
+        <v>876516</v>
       </c>
       <c r="R25" t="n">
-        <v>7396417</v>
+        <v>7396355</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120170136</v>
+        <v>120170140</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>876566</v>
+        <v>876678</v>
       </c>
       <c r="R26" t="n">
-        <v>7396402</v>
+        <v>7396446</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134339</v>
+        <v>120134337</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876579</v>
+        <v>876530</v>
       </c>
       <c r="R2" t="n">
-        <v>7396370</v>
+        <v>7396367</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134330</v>
+        <v>120134329</v>
       </c>
       <c r="B3" t="n">
-        <v>96891</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876589</v>
+        <v>876676</v>
       </c>
       <c r="R3" t="n">
-        <v>7396375</v>
+        <v>7396418</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134331</v>
+        <v>120134340</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876885</v>
+        <v>876586</v>
       </c>
       <c r="R4" t="n">
-        <v>7396474</v>
+        <v>7396380</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134337</v>
+        <v>120134330</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>96891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876530</v>
+        <v>876589</v>
       </c>
       <c r="R5" t="n">
-        <v>7396367</v>
+        <v>7396375</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134340</v>
+        <v>120134339</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876586</v>
+        <v>876579</v>
       </c>
       <c r="R7" t="n">
-        <v>7396380</v>
+        <v>7396370</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120134329</v>
+        <v>120134331</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876676</v>
+        <v>876885</v>
       </c>
       <c r="R8" t="n">
-        <v>7396418</v>
+        <v>7396474</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170125</v>
+        <v>120170102</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876716</v>
+        <v>876516</v>
       </c>
       <c r="R9" t="n">
-        <v>7396410</v>
+        <v>7396355</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170122</v>
+        <v>120170118</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876931</v>
+        <v>876442</v>
       </c>
       <c r="R10" t="n">
-        <v>7396534</v>
+        <v>7396355</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170120</v>
+        <v>120170119</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876442</v>
+        <v>876440</v>
       </c>
       <c r="R11" t="n">
-        <v>7396374</v>
+        <v>7396356</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170119</v>
+        <v>120170137</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876440</v>
+        <v>876569</v>
       </c>
       <c r="R12" t="n">
-        <v>7396356</v>
+        <v>7396417</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170105</v>
+        <v>120170125</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876569</v>
+        <v>876716</v>
       </c>
       <c r="R13" t="n">
-        <v>7396418</v>
+        <v>7396410</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170134</v>
+        <v>120170136</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876433</v>
+        <v>876566</v>
       </c>
       <c r="R14" t="n">
-        <v>7396336</v>
+        <v>7396402</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170136</v>
+        <v>120170120</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876566</v>
+        <v>876442</v>
       </c>
       <c r="R15" t="n">
-        <v>7396402</v>
+        <v>7396374</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170118</v>
+        <v>120170117</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876442</v>
+        <v>876887</v>
       </c>
       <c r="R16" t="n">
-        <v>7396355</v>
+        <v>7396479</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170135</v>
+        <v>120170122</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876452</v>
+        <v>876931</v>
       </c>
       <c r="R17" t="n">
-        <v>7396372</v>
+        <v>7396534</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170137</v>
+        <v>120170121</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876569</v>
+        <v>876428</v>
       </c>
       <c r="R18" t="n">
-        <v>7396417</v>
+        <v>7396353</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170108</v>
+        <v>120170134</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876568</v>
+        <v>876433</v>
       </c>
       <c r="R19" t="n">
-        <v>7396419</v>
+        <v>7396336</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2485,11 +2485,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170139</v>
+        <v>120170108</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876641</v>
+        <v>876568</v>
       </c>
       <c r="R20" t="n">
-        <v>7396423</v>
+        <v>7396419</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2592,6 +2587,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120170117</v>
+        <v>120170138</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>876887</v>
+        <v>876628</v>
       </c>
       <c r="R21" t="n">
-        <v>7396479</v>
+        <v>7396416</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120170138</v>
+        <v>120170139</v>
       </c>
       <c r="B22" t="n">
         <v>78542</v>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>876628</v>
+        <v>876641</v>
       </c>
       <c r="R22" t="n">
-        <v>7396416</v>
+        <v>7396423</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120170123</v>
+        <v>120170105</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>876887</v>
+        <v>876569</v>
       </c>
       <c r="R23" t="n">
-        <v>7396501</v>
+        <v>7396418</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120170121</v>
+        <v>120170140</v>
       </c>
       <c r="B24" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>876428</v>
+        <v>876678</v>
       </c>
       <c r="R24" t="n">
-        <v>7396353</v>
+        <v>7396446</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120170102</v>
+        <v>120170135</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>876516</v>
+        <v>876452</v>
       </c>
       <c r="R25" t="n">
-        <v>7396355</v>
+        <v>7396372</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120170140</v>
+        <v>120170123</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>876678</v>
+        <v>876887</v>
       </c>
       <c r="R26" t="n">
-        <v>7396446</v>
+        <v>7396501</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134337</v>
+        <v>120134341</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876530</v>
+        <v>876700</v>
       </c>
       <c r="R2" t="n">
-        <v>7396367</v>
+        <v>7396427</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134340</v>
+        <v>120134339</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876586</v>
+        <v>876579</v>
       </c>
       <c r="R4" t="n">
-        <v>7396380</v>
+        <v>7396370</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134330</v>
+        <v>120134340</v>
       </c>
       <c r="B5" t="n">
-        <v>96891</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876589</v>
+        <v>876586</v>
       </c>
       <c r="R5" t="n">
-        <v>7396375</v>
+        <v>7396380</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134341</v>
+        <v>120134337</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876700</v>
+        <v>876530</v>
       </c>
       <c r="R6" t="n">
-        <v>7396427</v>
+        <v>7396367</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134339</v>
+        <v>120134330</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>96891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876579</v>
+        <v>876589</v>
       </c>
       <c r="R7" t="n">
-        <v>7396370</v>
+        <v>7396375</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170102</v>
+        <v>120170122</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876516</v>
+        <v>876931</v>
       </c>
       <c r="R9" t="n">
-        <v>7396355</v>
+        <v>7396534</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170118</v>
+        <v>120170123</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876442</v>
+        <v>876887</v>
       </c>
       <c r="R10" t="n">
-        <v>7396355</v>
+        <v>7396501</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170119</v>
+        <v>120170138</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876440</v>
+        <v>876628</v>
       </c>
       <c r="R11" t="n">
-        <v>7396356</v>
+        <v>7396416</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170137</v>
+        <v>120170125</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876569</v>
+        <v>876716</v>
       </c>
       <c r="R12" t="n">
-        <v>7396417</v>
+        <v>7396410</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170125</v>
+        <v>120170135</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876716</v>
+        <v>876452</v>
       </c>
       <c r="R13" t="n">
-        <v>7396410</v>
+        <v>7396372</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170136</v>
+        <v>120170118</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876566</v>
+        <v>876442</v>
       </c>
       <c r="R14" t="n">
-        <v>7396402</v>
+        <v>7396355</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170120</v>
+        <v>120170108</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876442</v>
+        <v>876568</v>
       </c>
       <c r="R15" t="n">
-        <v>7396374</v>
+        <v>7396419</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2077,6 +2077,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170117</v>
+        <v>120170136</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876887</v>
+        <v>876566</v>
       </c>
       <c r="R16" t="n">
-        <v>7396479</v>
+        <v>7396402</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170122</v>
+        <v>120170121</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876931</v>
+        <v>876428</v>
       </c>
       <c r="R17" t="n">
-        <v>7396534</v>
+        <v>7396353</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2307,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170121</v>
+        <v>120170120</v>
       </c>
       <c r="B18" t="n">
-        <v>90594</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876428</v>
+        <v>876442</v>
       </c>
       <c r="R18" t="n">
-        <v>7396353</v>
+        <v>7396374</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2409,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170134</v>
+        <v>120170105</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876433</v>
+        <v>876569</v>
       </c>
       <c r="R19" t="n">
-        <v>7396336</v>
+        <v>7396418</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2511,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170108</v>
+        <v>120170140</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876568</v>
+        <v>876678</v>
       </c>
       <c r="R20" t="n">
-        <v>7396419</v>
+        <v>7396446</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2587,11 +2592,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120170138</v>
+        <v>120170119</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>876628</v>
+        <v>876440</v>
       </c>
       <c r="R21" t="n">
-        <v>7396416</v>
+        <v>7396356</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120170105</v>
+        <v>120170137</v>
       </c>
       <c r="B23" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
         <v>876569</v>
       </c>
       <c r="R23" t="n">
-        <v>7396418</v>
+        <v>7396417</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2924,7 +2924,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120170140</v>
+        <v>120170134</v>
       </c>
       <c r="B24" t="n">
         <v>78542</v>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>876678</v>
+        <v>876433</v>
       </c>
       <c r="R24" t="n">
-        <v>7396446</v>
+        <v>7396336</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120170135</v>
+        <v>120170102</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>876452</v>
+        <v>876516</v>
       </c>
       <c r="R25" t="n">
-        <v>7396372</v>
+        <v>7396355</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120170123</v>
+        <v>120170117</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,25 +3140,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3171,7 +3171,7 @@
         <v>876887</v>
       </c>
       <c r="R26" t="n">
-        <v>7396501</v>
+        <v>7396479</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134341</v>
+        <v>120134339</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876700</v>
+        <v>876579</v>
       </c>
       <c r="R2" t="n">
-        <v>7396427</v>
+        <v>7396370</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134329</v>
+        <v>120134337</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876676</v>
+        <v>876530</v>
       </c>
       <c r="R3" t="n">
-        <v>7396418</v>
+        <v>7396367</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134339</v>
+        <v>120134340</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876579</v>
+        <v>876586</v>
       </c>
       <c r="R4" t="n">
-        <v>7396370</v>
+        <v>7396380</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134340</v>
+        <v>120134331</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876586</v>
+        <v>876885</v>
       </c>
       <c r="R5" t="n">
-        <v>7396380</v>
+        <v>7396474</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134337</v>
+        <v>120134329</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876530</v>
+        <v>876676</v>
       </c>
       <c r="R6" t="n">
-        <v>7396367</v>
+        <v>7396418</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134330</v>
+        <v>120134341</v>
       </c>
       <c r="B7" t="n">
-        <v>96891</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876589</v>
+        <v>876700</v>
       </c>
       <c r="R7" t="n">
-        <v>7396375</v>
+        <v>7396427</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120134331</v>
+        <v>120134330</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>96891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876885</v>
+        <v>876589</v>
       </c>
       <c r="R8" t="n">
-        <v>7396474</v>
+        <v>7396375</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170122</v>
+        <v>120170119</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876931</v>
+        <v>876440</v>
       </c>
       <c r="R9" t="n">
-        <v>7396534</v>
+        <v>7396356</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170123</v>
+        <v>120170134</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876887</v>
+        <v>876433</v>
       </c>
       <c r="R10" t="n">
-        <v>7396501</v>
+        <v>7396336</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170138</v>
+        <v>120170135</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876628</v>
+        <v>876452</v>
       </c>
       <c r="R11" t="n">
-        <v>7396416</v>
+        <v>7396372</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170125</v>
+        <v>120170139</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876716</v>
+        <v>876641</v>
       </c>
       <c r="R12" t="n">
-        <v>7396410</v>
+        <v>7396423</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170135</v>
+        <v>120170108</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876452</v>
+        <v>876568</v>
       </c>
       <c r="R13" t="n">
-        <v>7396372</v>
+        <v>7396419</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1873,6 +1873,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170118</v>
+        <v>120170120</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -1942,7 +1947,7 @@
         <v>876442</v>
       </c>
       <c r="R14" t="n">
-        <v>7396355</v>
+        <v>7396374</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170108</v>
+        <v>120170117</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876568</v>
+        <v>876887</v>
       </c>
       <c r="R15" t="n">
-        <v>7396419</v>
+        <v>7396479</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2077,11 +2082,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170136</v>
+        <v>120170121</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876566</v>
+        <v>876428</v>
       </c>
       <c r="R16" t="n">
-        <v>7396402</v>
+        <v>7396353</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170121</v>
+        <v>120170136</v>
       </c>
       <c r="B17" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876428</v>
+        <v>876566</v>
       </c>
       <c r="R17" t="n">
-        <v>7396353</v>
+        <v>7396402</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170120</v>
+        <v>120170102</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876442</v>
+        <v>876516</v>
       </c>
       <c r="R18" t="n">
-        <v>7396374</v>
+        <v>7396355</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170105</v>
+        <v>120170125</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876569</v>
+        <v>876716</v>
       </c>
       <c r="R19" t="n">
-        <v>7396418</v>
+        <v>7396410</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170140</v>
+        <v>120170137</v>
       </c>
       <c r="B20" t="n">
         <v>78542</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876678</v>
+        <v>876569</v>
       </c>
       <c r="R20" t="n">
-        <v>7396446</v>
+        <v>7396417</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120170119</v>
+        <v>120170138</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>876440</v>
+        <v>876628</v>
       </c>
       <c r="R21" t="n">
-        <v>7396356</v>
+        <v>7396416</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120170139</v>
+        <v>120170122</v>
       </c>
       <c r="B22" t="n">
         <v>78542</v>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>876641</v>
+        <v>876931</v>
       </c>
       <c r="R22" t="n">
-        <v>7396423</v>
+        <v>7396534</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120170137</v>
+        <v>120170123</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>876569</v>
+        <v>876887</v>
       </c>
       <c r="R23" t="n">
-        <v>7396417</v>
+        <v>7396501</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120170134</v>
+        <v>120170118</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>876433</v>
+        <v>876442</v>
       </c>
       <c r="R24" t="n">
-        <v>7396336</v>
+        <v>7396355</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120170102</v>
+        <v>120170105</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>876516</v>
+        <v>876569</v>
       </c>
       <c r="R25" t="n">
-        <v>7396355</v>
+        <v>7396418</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120170117</v>
+        <v>120170140</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,25 +3140,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>876887</v>
+        <v>876678</v>
       </c>
       <c r="R26" t="n">
-        <v>7396479</v>
+        <v>7396446</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134339</v>
+        <v>120134330</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>96891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876579</v>
+        <v>876589</v>
       </c>
       <c r="R2" t="n">
-        <v>7396370</v>
+        <v>7396375</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134337</v>
+        <v>120134340</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876530</v>
+        <v>876586</v>
       </c>
       <c r="R3" t="n">
-        <v>7396367</v>
+        <v>7396380</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134340</v>
+        <v>120134341</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876586</v>
+        <v>876700</v>
       </c>
       <c r="R4" t="n">
-        <v>7396380</v>
+        <v>7396427</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134331</v>
+        <v>120134329</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876885</v>
+        <v>876676</v>
       </c>
       <c r="R5" t="n">
-        <v>7396474</v>
+        <v>7396418</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134329</v>
+        <v>120134339</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876676</v>
+        <v>876579</v>
       </c>
       <c r="R6" t="n">
-        <v>7396418</v>
+        <v>7396370</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134341</v>
+        <v>120134337</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876700</v>
+        <v>876530</v>
       </c>
       <c r="R7" t="n">
-        <v>7396427</v>
+        <v>7396367</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120134330</v>
+        <v>120134331</v>
       </c>
       <c r="B8" t="n">
-        <v>96891</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876589</v>
+        <v>876885</v>
       </c>
       <c r="R8" t="n">
-        <v>7396375</v>
+        <v>7396474</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170119</v>
+        <v>120170136</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876440</v>
+        <v>876566</v>
       </c>
       <c r="R9" t="n">
-        <v>7396356</v>
+        <v>7396402</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170134</v>
+        <v>120170140</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876433</v>
+        <v>876678</v>
       </c>
       <c r="R10" t="n">
-        <v>7396336</v>
+        <v>7396446</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170135</v>
+        <v>120170121</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876452</v>
+        <v>876428</v>
       </c>
       <c r="R11" t="n">
-        <v>7396372</v>
+        <v>7396353</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170139</v>
+        <v>120170105</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876641</v>
+        <v>876569</v>
       </c>
       <c r="R12" t="n">
-        <v>7396423</v>
+        <v>7396418</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170108</v>
+        <v>120170120</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876568</v>
+        <v>876442</v>
       </c>
       <c r="R13" t="n">
-        <v>7396419</v>
+        <v>7396374</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1873,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170120</v>
+        <v>120170117</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876442</v>
+        <v>876887</v>
       </c>
       <c r="R14" t="n">
-        <v>7396374</v>
+        <v>7396479</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170117</v>
+        <v>120170137</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876887</v>
+        <v>876569</v>
       </c>
       <c r="R15" t="n">
-        <v>7396479</v>
+        <v>7396417</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170121</v>
+        <v>120170108</v>
       </c>
       <c r="B16" t="n">
-        <v>90594</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876428</v>
+        <v>876568</v>
       </c>
       <c r="R16" t="n">
-        <v>7396353</v>
+        <v>7396419</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2184,6 +2179,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2210,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170136</v>
+        <v>120170134</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876566</v>
+        <v>876433</v>
       </c>
       <c r="R17" t="n">
-        <v>7396402</v>
+        <v>7396336</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170102</v>
+        <v>120170118</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876516</v>
+        <v>876442</v>
       </c>
       <c r="R18" t="n">
         <v>7396355</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170125</v>
+        <v>120170123</v>
       </c>
       <c r="B19" t="n">
         <v>78542</v>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876716</v>
+        <v>876887</v>
       </c>
       <c r="R19" t="n">
-        <v>7396410</v>
+        <v>7396501</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170137</v>
+        <v>120170139</v>
       </c>
       <c r="B20" t="n">
         <v>78542</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876569</v>
+        <v>876641</v>
       </c>
       <c r="R20" t="n">
-        <v>7396417</v>
+        <v>7396423</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120170138</v>
+        <v>120170122</v>
       </c>
       <c r="B21" t="n">
         <v>78542</v>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>876628</v>
+        <v>876931</v>
       </c>
       <c r="R21" t="n">
-        <v>7396416</v>
+        <v>7396534</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120170122</v>
+        <v>120170138</v>
       </c>
       <c r="B22" t="n">
         <v>78542</v>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>876931</v>
+        <v>876628</v>
       </c>
       <c r="R22" t="n">
-        <v>7396534</v>
+        <v>7396416</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120170123</v>
+        <v>120170135</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>876887</v>
+        <v>876452</v>
       </c>
       <c r="R23" t="n">
-        <v>7396501</v>
+        <v>7396372</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120170118</v>
+        <v>120170125</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>876442</v>
+        <v>876716</v>
       </c>
       <c r="R24" t="n">
-        <v>7396355</v>
+        <v>7396410</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120170105</v>
+        <v>120170119</v>
       </c>
       <c r="B25" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>876569</v>
+        <v>876440</v>
       </c>
       <c r="R25" t="n">
-        <v>7396418</v>
+        <v>7396356</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120170140</v>
+        <v>120170102</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>876678</v>
+        <v>876516</v>
       </c>
       <c r="R26" t="n">
-        <v>7396446</v>
+        <v>7396355</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170140</v>
+        <v>120170121</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876678</v>
+        <v>876428</v>
       </c>
       <c r="R10" t="n">
-        <v>7396446</v>
+        <v>7396353</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170121</v>
+        <v>120170140</v>
       </c>
       <c r="B11" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876428</v>
+        <v>876678</v>
       </c>
       <c r="R11" t="n">
-        <v>7396353</v>
+        <v>7396446</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134340</v>
+        <v>120170102</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hanhinoja, Nb</t>
+          <t>Hanhivaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876586</v>
+        <v>876516</v>
       </c>
       <c r="R2" t="n">
-        <v>7396380</v>
+        <v>7396355</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134330</v>
+        <v>120170121</v>
       </c>
       <c r="B3" t="n">
-        <v>96891</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hanhinoja, Nb</t>
+          <t>Hanhivaara, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876589</v>
+        <v>876428</v>
       </c>
       <c r="R3" t="n">
-        <v>7396375</v>
+        <v>7396353</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,62 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134329</v>
+        <v>120170142</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hanhinoja, Nb</t>
+          <t>Hanhivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876676</v>
+        <v>876759</v>
       </c>
       <c r="R4" t="n">
-        <v>7396418</v>
+        <v>7396408</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -963,33 +948,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134337</v>
+        <v>120170112</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +978,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hanhinoja, Nb</t>
+          <t>Hanhivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876530</v>
+        <v>876826</v>
       </c>
       <c r="R5" t="n">
-        <v>7396367</v>
+        <v>7396430</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1071,27 +1052,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134339</v>
+        <v>120170114</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1075,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hanhinoja, Nb</t>
+          <t>Hanhivaara, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876579</v>
+        <v>876815</v>
       </c>
       <c r="R6" t="n">
-        <v>7396370</v>
+        <v>7396407</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,31 +1149,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134341</v>
+        <v>120134337</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1225,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876700</v>
+        <v>876530</v>
       </c>
       <c r="R7" t="n">
-        <v>7396427</v>
+        <v>7396367</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,15 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120134331</v>
+        <v>120134339</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1269,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876885</v>
+        <v>876579</v>
       </c>
       <c r="R8" t="n">
-        <v>7396474</v>
+        <v>7396370</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,50 +1355,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170108</v>
+        <v>120134340</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hanhivaara, Nb</t>
+          <t>Hanhinoja, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876568</v>
+        <v>876586</v>
       </c>
       <c r="R9" t="n">
-        <v>7396419</v>
+        <v>7396380</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1467,11 +1428,6 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1484,31 +1440,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170138</v>
+        <v>120134341</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1532,14 +1483,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hanhivaara, Nb</t>
+          <t>Hanhinoja, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876628</v>
+        <v>876700</v>
       </c>
       <c r="R10" t="n">
-        <v>7396416</v>
+        <v>7396427</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1586,27 +1537,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170119</v>
+        <v>120170122</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1560,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876440</v>
+        <v>876931</v>
       </c>
       <c r="R11" t="n">
-        <v>7396356</v>
+        <v>7396534</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1700,19 +1646,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170122</v>
+        <v>120170123</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1740,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876931</v>
+        <v>876887</v>
       </c>
       <c r="R12" t="n">
-        <v>7396534</v>
+        <v>7396501</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1802,19 +1743,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170134</v>
+        <v>120170125</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1842,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876433</v>
+        <v>876716</v>
       </c>
       <c r="R13" t="n">
-        <v>7396336</v>
+        <v>7396410</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1904,19 +1840,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170137</v>
+        <v>120170134</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1944,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876569</v>
+        <v>876433</v>
       </c>
       <c r="R14" t="n">
-        <v>7396417</v>
+        <v>7396336</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2006,19 +1937,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170125</v>
+        <v>120170135</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2046,10 +1972,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876716</v>
+        <v>876452</v>
       </c>
       <c r="R15" t="n">
-        <v>7396410</v>
+        <v>7396372</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2108,15 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170118</v>
+        <v>120170136</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,21 +2045,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876442</v>
+        <v>876566</v>
       </c>
       <c r="R16" t="n">
-        <v>7396355</v>
+        <v>7396402</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2210,19 +2131,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170135</v>
+        <v>120170137</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2250,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876452</v>
+        <v>876569</v>
       </c>
       <c r="R17" t="n">
-        <v>7396372</v>
+        <v>7396417</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2312,37 +2228,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170121</v>
+        <v>120170138</v>
       </c>
       <c r="B18" t="n">
-        <v>90594</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876428</v>
+        <v>876628</v>
       </c>
       <c r="R18" t="n">
-        <v>7396353</v>
+        <v>7396416</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2414,37 +2325,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170105</v>
+        <v>120170139</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2360,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876569</v>
+        <v>876641</v>
       </c>
       <c r="R19" t="n">
-        <v>7396418</v>
+        <v>7396423</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2519,16 +2425,11 @@
         <v>120170140</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2618,19 +2519,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120170123</v>
+        <v>120170141</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2658,10 +2554,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>876887</v>
+        <v>876809</v>
       </c>
       <c r="R21" t="n">
-        <v>7396501</v>
+        <v>7396415</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2720,37 +2616,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120170120</v>
+        <v>120170115</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2651,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>876442</v>
+        <v>876768</v>
       </c>
       <c r="R22" t="n">
-        <v>7396374</v>
+        <v>7396405</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2822,50 +2713,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120170117</v>
+        <v>120134329</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hanhivaara, Nb</t>
+          <t>Hanhinoja, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>876887</v>
+        <v>876676</v>
       </c>
       <c r="R23" t="n">
-        <v>7396479</v>
+        <v>7396418</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2912,49 +2798,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120170136</v>
+        <v>120170108</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2845,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>876566</v>
+        <v>876568</v>
       </c>
       <c r="R24" t="n">
-        <v>7396402</v>
+        <v>7396419</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3000,6 +2881,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3026,15 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120170102</v>
+        <v>120170105</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,21 +2923,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>876516</v>
+        <v>876569</v>
       </c>
       <c r="R25" t="n">
-        <v>7396355</v>
+        <v>7396418</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3128,50 +3009,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120170139</v>
+        <v>120134331</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hanhivaara, Nb</t>
+          <t>Hanhinoja, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>876641</v>
+        <v>876885</v>
       </c>
       <c r="R26" t="n">
-        <v>7396423</v>
+        <v>7396474</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3218,15 +3094,500 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120170117</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>876887</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7396479</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120170118</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>876442</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7396355</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120170119</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>876440</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7396356</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120170120</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>876442</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7396374</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120134330</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hanhinoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>876589</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7396375</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41915-2024 artfynd.xlsx
+++ b/artfynd/A 41915-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170102</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170121</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170142</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170112</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170114</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120134337</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120134339</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120134340</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120134341</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170122</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170123</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170125</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170134</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170135</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170136</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2225,6 +2305,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170137</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2322,6 +2407,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170138</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2419,6 +2509,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170139</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2516,6 +2611,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170140</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2613,6 +2713,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170141</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2710,6 +2815,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170115</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2807,6 +2917,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120134329</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2909,6 +3024,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170108</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3006,6 +3126,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170105</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3103,6 +3228,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120134331</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3200,6 +3330,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170117</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3297,6 +3432,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170118</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3394,6 +3534,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170119</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3491,6 +3636,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120170120</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3588,8 +3738,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120134330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>